--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1604,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1884,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3354,34 +3350,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3572,7 +3564,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4478,34 +4470,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5256,7 +5244,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6660,7 +6648,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -9246,34 +9234,30 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10346,34 +10330,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12812,7 +12792,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -13372,7 +13352,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13652,7 +13632,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -18416,7 +18396,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -19536,7 +19516,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21816,28 +21796,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22654,34 +22638,30 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22938,34 +22918,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23156,7 +23132,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23972,7 +23948,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -26196,7 +26172,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -29768,7 +29744,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -31424,7 +31400,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -38916,7 +38892,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -39476,7 +39452,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -44534,34 +44510,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47736,7 +47708,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -51184,34 +51156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -51962,7 +51930,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -52242,7 +52210,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -53712,34 +53680,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -53930,7 +53894,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -54836,34 +54800,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -55614,7 +55574,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-19.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-19.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19352,7 +19352,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -28590,7 +28590,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -30806,7 +30806,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
